--- a/data/besoins_production.xlsx
+++ b/data/besoins_production.xlsx
@@ -1,49 +1,142 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/58830f9fc3ba735f/Documents/pilotage-stock-production/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2B59D2BFD300DD8AB9495A33469528F06A3DFB0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D111D67-8C96-4F06-8017-AC5B025456F1}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+  <si>
+    <t>code_matiere</t>
+  </si>
+  <si>
+    <t>ligne_production</t>
+  </si>
+  <si>
+    <t>quantite_demandee</t>
+  </si>
+  <si>
+    <t>date_besoin</t>
+  </si>
+  <si>
+    <t>criticite</t>
+  </si>
+  <si>
+    <t>commentaire</t>
+  </si>
+  <si>
+    <t>statut</t>
+  </si>
+  <si>
+    <t>ART059</t>
+  </si>
+  <si>
+    <t>Ligne A</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>Haute (5)</t>
+  </si>
+  <si>
+    <t>À traiter</t>
+  </si>
+  <si>
+    <t>ART001</t>
+  </si>
+  <si>
+    <t>Ligne B</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>Haute (4)</t>
+  </si>
+  <si>
+    <t>ART005</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>Moyenne (3)</t>
+  </si>
+  <si>
+    <t>ART002</t>
+  </si>
+  <si>
+    <t>Ligne C</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>Normale (2)</t>
+  </si>
+  <si>
+    <t>ART006</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>Basse (1)</t>
+  </si>
+  <si>
+    <t>ART009</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
-        <bgColor rgb="002F5496"/>
+        <fgColor rgb="FF2F5496"/>
+        <bgColor rgb="FF2F5496"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,85 +153,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -426,236 +464,159 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="16" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21" style="2" customWidth="1"/>
+    <col min="4" max="4" width="23" style="2" customWidth="1"/>
+    <col min="5" max="6" width="15" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>code_matiere</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>ligne_production</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>quantite_demandee</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>date_besoin</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>criticite</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>commentaire</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>statut</t>
-        </is>
+    <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ART059</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ligne A</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
         <v>50</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Haute (5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>À traiter</t>
-        </is>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ART001</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ligne B</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2">
         <v>20</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Haute (4)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>À traiter</t>
-        </is>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ART005</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ligne A</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
         <v>15</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Moyenne (3)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>À traiter</t>
-        </is>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ART002</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ligne C</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2">
         <v>10</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Normale (2)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>À traiter</t>
-        </is>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ART006</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ligne B</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2">
         <v>30</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Basse (1)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>À traiter</t>
-        </is>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ART009</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ligne A</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2">
         <v>80</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="3">
         <v>46213</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Moyenne (3)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>À traiter</t>
-        </is>
+      <c r="E7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/besoins_production.xlsx
+++ b/data/besoins_production.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/58830f9fc3ba735f/Documents/pilotage-stock-production/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\israc\OneDrive\Documents\pilotage-stock-production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_2B59D2BFD300DD8AB9495A33469528F06A3DFB0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D111D67-8C96-4F06-8017-AC5B025456F1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C048D428-2514-4DB8-9AB0-D00A36BF86FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="besoin production" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/data/besoins_production.xlsx
+++ b/data/besoins_production.xlsx
@@ -1,142 +1,74 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\israc\OneDrive\Documents\pilotage-stock-production\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C048D428-2514-4DB8-9AB0-D00A36BF86FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="besoin production" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="besoin production" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
-  <si>
-    <t>code_matiere</t>
-  </si>
-  <si>
-    <t>ligne_production</t>
-  </si>
-  <si>
-    <t>quantite_demandee</t>
-  </si>
-  <si>
-    <t>date_besoin</t>
-  </si>
-  <si>
-    <t>criticite</t>
-  </si>
-  <si>
-    <t>commentaire</t>
-  </si>
-  <si>
-    <t>statut</t>
-  </si>
-  <si>
-    <t>ART059</t>
-  </si>
-  <si>
-    <t>Ligne A</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>Haute (5)</t>
-  </si>
-  <si>
-    <t>À traiter</t>
-  </si>
-  <si>
-    <t>ART001</t>
-  </si>
-  <si>
-    <t>Ligne B</t>
-  </si>
-  <si>
-    <t>2026-07-05</t>
-  </si>
-  <si>
-    <t>Haute (4)</t>
-  </si>
-  <si>
-    <t>ART005</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>Moyenne (3)</t>
-  </si>
-  <si>
-    <t>ART002</t>
-  </si>
-  <si>
-    <t>Ligne C</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>Normale (2)</t>
-  </si>
-  <si>
-    <t>ART006</t>
-  </si>
-  <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
-    <t>Basse (1)</t>
-  </si>
-  <si>
-    <t>ART009</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5496"/>
-        <bgColor rgb="FF2F5496"/>
+        <fgColor rgb="00305496"/>
+        <bgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -152,31 +84,90 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -464,159 +455,414 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20" style="2" customWidth="1"/>
-    <col min="3" max="3" width="21" style="2" customWidth="1"/>
-    <col min="4" max="4" width="23" style="2" customWidth="1"/>
-    <col min="5" max="6" width="15" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13" style="2" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>code_matiere</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>designation_matiere</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ligne_production</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>quantite_demandee</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>date_besoin</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>criticite</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>commentaire</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ancien_code_matiere</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>confiance_mapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PEFEC</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>FUT EN CARTON | 357x280x10</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Ligne A</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Haute (5)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>À traiter</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>ART059</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CP3GC-PR4.0</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRANTAGES | 150x90x15 | PR4.0 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Ligne B</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Haute (4)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>À traiter</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>ART001</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CP3GC-PR7.0</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRANTAGES | 150x90x15 | PR7.0 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Ligne A</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Moyenne (3)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>À traiter</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>ART005</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CP3GC-PR5.0</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>JEU DE 3 GALETS DE CRANTAGES | 150x90x15 | PR5.0 | CARB-TUNGS</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Ligne C</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2">
-        <v>20</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Normale (2)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>À traiter</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>ART002</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CPBSM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>BROSSE SPIRALE METALLIQUE | 60x1000</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Ligne B</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Basse (1)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>À traiter</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ART006</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CPHDC</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>HUILE DE COUPE SOLUBLE DANS L'EAU</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Ligne A</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E7" s="5" t="n">
         <v>46213</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>11</v>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Moyenne (3)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>À traiter</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>ART009</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>moyenne</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Notes sur la mise à jour des codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Les codes ART0xx (anciennes données factices) ont été remplacés par les vrais codes AX de matieres.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ancien_code_matiere est conservé pour traçabilité.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>confiance_mapping : haute = correspondance quasi certaine ; moyenne = correspondance probable, à vérifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Les autres colonnes (quantite_demandee, date_besoin, criticite, statut) restent des données FACTICES, non remplacées.</t>
+        </is>
       </c>
     </row>
   </sheetData>
